--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFED189-6474-4A12-96B4-D7115E687D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA0BD08-2D01-4128-998D-ECC2B15CF673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
@@ -1417,6 +1417,7 @@
       <c r="J70" s="2"/>
       <c r="L70" s="2"/>
     </row>
+    <row r="71" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB45F6E-7049-4106-A45D-7DDB272945C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -408,7 +409,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -531,9 +532,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -545,6 +543,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -822,20 +823,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:XFD84"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="12.25" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="7" width="16.75" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" customWidth="1"/>
     <col min="8" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="21.5" customWidth="1"/>
-    <col min="11" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" customWidth="1"/>
+    <col min="11" max="12" width="13.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384">
@@ -866,15 +867,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
     </row>
     <row r="2" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384">
       <c r="A2" s="1" t="s">
@@ -17468,7 +17469,7 @@
       <c r="XFB13" s="2"/>
       <c r="XFD13" s="2"/>
     </row>
-    <row r="14" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" ht="13.15" customHeight="1">
+    <row r="14" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" ht="13.2" customHeight="1">
       <c r="B14" s="2" t="s">
         <v>64</v>
       </c>
@@ -17483,12 +17484,12 @@
       </c>
       <c r="P14" s="2"/>
     </row>
-    <row r="15" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" s="8" customFormat="1">
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="P15" s="9"/>
+    <row r="15" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" s="7" customFormat="1">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="P15" s="8"/>
     </row>
     <row r="16" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384">
       <c r="B16" s="2" t="s">
@@ -17529,12 +17530,12 @@
       </c>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="2:16" s="8" customFormat="1">
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="P19" s="9"/>
+    <row r="19" spans="2:16" s="7" customFormat="1">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="P19" s="8"/>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" s="2" t="s">
@@ -17562,12 +17563,12 @@
       </c>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="2:16" s="8" customFormat="1">
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="P22" s="9"/>
+    <row r="22" spans="2:16" s="7" customFormat="1">
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="P22" s="8"/>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" s="2" t="s">
@@ -17595,12 +17596,12 @@
       </c>
       <c r="P24" s="2"/>
     </row>
-    <row r="25" spans="2:16" s="8" customFormat="1">
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="P25" s="9"/>
+    <row r="25" spans="2:16" s="7" customFormat="1">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" s="2" t="s">
@@ -17628,12 +17629,12 @@
       </c>
       <c r="P27" s="2"/>
     </row>
-    <row r="28" spans="2:16" s="8" customFormat="1">
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="P28" s="9"/>
+    <row r="28" spans="2:16" s="7" customFormat="1">
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="P28" s="8"/>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" s="2" t="s">
@@ -17734,11 +17735,11 @@
       <c r="M33" s="2"/>
       <c r="P33" s="2"/>
     </row>
-    <row r="34" spans="2:16" s="8" customFormat="1">
-      <c r="B34" s="10"/>
-      <c r="C34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="P34" s="9"/>
+    <row r="34" spans="2:16" s="7" customFormat="1">
+      <c r="B34" s="9"/>
+      <c r="C34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="P34" s="8"/>
     </row>
     <row r="35" spans="2:16" s="2" customFormat="1">
       <c r="B35" s="2" t="s">
@@ -17756,14 +17757,14 @@
     </row>
     <row r="36" spans="2:16" s="2" customFormat="1">
       <c r="J36" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="37" spans="2:16">
-      <c r="B37" s="7"/>
+      <c r="B37" s="6"/>
       <c r="C37" s="2"/>
       <c r="K37" s="2"/>
       <c r="P37" s="2"/>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB45F6E-7049-4106-A45D-7DDB272945C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8235022C-D178-4F06-88CF-8FB91C82EB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="107">
   <si>
     <t>##var</t>
   </si>
@@ -405,6 +405,34 @@
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>MMCAttributeBased</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttributeBasedMmcParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttrSetCode</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttrCode</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FromType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CaptureType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -513,7 +541,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -530,9 +558,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
@@ -824,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:XFD84"/>
+  <dimension ref="A1:XFD90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
@@ -867,15 +892,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
     </row>
     <row r="2" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384">
       <c r="A2" s="1" t="s">
@@ -17484,12 +17509,12 @@
       </c>
       <c r="P14" s="2"/>
     </row>
-    <row r="15" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" s="7" customFormat="1">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="P15" s="8"/>
+    <row r="15" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" s="6" customFormat="1">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="P15" s="7"/>
     </row>
     <row r="16" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384">
       <c r="B16" s="2" t="s">
@@ -17530,12 +17555,12 @@
       </c>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="2:16" s="7" customFormat="1">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="P19" s="8"/>
+    <row r="19" spans="2:16" s="6" customFormat="1">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="P19" s="7"/>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" s="2" t="s">
@@ -17563,12 +17588,12 @@
       </c>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="2:16" s="7" customFormat="1">
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="P22" s="8"/>
+    <row r="22" spans="2:16" s="6" customFormat="1">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="P22" s="7"/>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" s="2" t="s">
@@ -17596,12 +17621,12 @@
       </c>
       <c r="P24" s="2"/>
     </row>
-    <row r="25" spans="2:16" s="7" customFormat="1">
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="P25" s="8"/>
+    <row r="25" spans="2:16" s="6" customFormat="1">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="P25" s="7"/>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" s="2" t="s">
@@ -17629,12 +17654,12 @@
       </c>
       <c r="P27" s="2"/>
     </row>
-    <row r="28" spans="2:16" s="7" customFormat="1">
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="P28" s="8"/>
+    <row r="28" spans="2:16" s="6" customFormat="1">
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="P28" s="7"/>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" s="2" t="s">
@@ -17735,11 +17760,11 @@
       <c r="M33" s="2"/>
       <c r="P33" s="2"/>
     </row>
-    <row r="34" spans="2:16" s="7" customFormat="1">
-      <c r="B34" s="9"/>
-      <c r="C34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="P34" s="8"/>
+    <row r="34" spans="2:16" s="6" customFormat="1">
+      <c r="B34" s="8"/>
+      <c r="C34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="P34" s="7"/>
     </row>
     <row r="35" spans="2:16" s="2" customFormat="1">
       <c r="B35" s="2" t="s">
@@ -17763,358 +17788,442 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="2:16">
-      <c r="B37" s="6"/>
-      <c r="C37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="P37" s="2"/>
+    <row r="37" spans="2:16" s="7" customFormat="1"/>
+    <row r="38" spans="2:16" customFormat="1">
+      <c r="B38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="J38" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P38" s="2"/>
     </row>
-    <row r="38" spans="2:16" s="3" customFormat="1"/>
-    <row r="39" spans="2:16">
-      <c r="B39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="L39" s="2"/>
+    <row r="39" spans="2:16" customFormat="1">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="J39" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P39" s="2"/>
     </row>
-    <row r="40" spans="2:16">
-      <c r="B40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="2"/>
+    <row r="40" spans="2:16" customFormat="1">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
       <c r="J40" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="K40" s="2"/>
       <c r="L40" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="P40" s="2"/>
     </row>
-    <row r="41" spans="2:16">
-      <c r="B41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="2"/>
+    <row r="41" spans="2:16" customFormat="1">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
       <c r="J41" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="K41" s="2"/>
       <c r="L41" s="2" t="s">
-        <v>67</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="P41" s="2"/>
     </row>
-    <row r="42" spans="2:16">
-      <c r="B42" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="2"/>
+    <row r="42" spans="2:16" customFormat="1">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
       <c r="J42" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="K42" s="2"/>
       <c r="L42" s="2" t="s">
-        <v>69</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="P42" s="2"/>
     </row>
-    <row r="43" spans="2:16">
+    <row r="43" spans="2:16" customFormat="1">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="L43" s="2"/>
+      <c r="J43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P43" s="2"/>
     </row>
-    <row r="44" spans="2:16" ht="21" customHeight="1">
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" spans="2:16" ht="15" customHeight="1">
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
+    <row r="44" spans="2:16" s="3" customFormat="1"/>
+    <row r="45" spans="2:16" customFormat="1">
+      <c r="B45" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="E45" s="2"/>
       <c r="J45" s="2"/>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" spans="2:16">
-      <c r="J46" s="2"/>
-      <c r="L46" s="2"/>
+    <row r="46" spans="2:16" customFormat="1">
+      <c r="B46" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="J46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="47" spans="2:16" ht="15" customHeight="1">
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
+    <row r="47" spans="2:16" customFormat="1">
+      <c r="B47" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="E47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="L47" s="2"/>
+      <c r="J47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="48" spans="2:16">
-      <c r="J48" s="2"/>
-      <c r="L48" s="2"/>
+    <row r="48" spans="2:16" customFormat="1">
+      <c r="B48" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="J48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="49" spans="2:12">
+    <row r="49" spans="2:12" customFormat="1">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="E49" s="2"/>
       <c r="J49" s="2"/>
       <c r="L49" s="2"/>
     </row>
-    <row r="50" spans="2:12" s="3" customFormat="1"/>
-    <row r="51" spans="2:12">
-      <c r="B51" t="s">
+    <row r="50" spans="2:12" customFormat="1" ht="21" customHeight="1">
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" spans="2:12" customFormat="1" ht="15" customHeight="1">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" spans="2:12" customFormat="1">
+      <c r="J52" s="2"/>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" spans="2:12" customFormat="1" ht="15" customHeight="1">
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" spans="2:12" customFormat="1">
+      <c r="J54" s="2"/>
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" spans="2:12" customFormat="1">
+      <c r="J55" s="2"/>
+      <c r="L55" s="2"/>
+    </row>
+    <row r="56" spans="2:12" s="3" customFormat="1"/>
+    <row r="57" spans="2:12" customFormat="1">
+      <c r="B57" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="2:12">
-      <c r="B52" s="2" t="s">
+    <row r="58" spans="2:12" customFormat="1">
+      <c r="B58" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C58" t="s">
         <v>26</v>
       </c>
-      <c r="J52" s="2" t="s">
+      <c r="J58" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L52" s="2" t="s">
+      <c r="L58" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="2:12" s="3" customFormat="1"/>
-    <row r="61" spans="2:12">
-      <c r="B61" s="2" t="s">
+    <row r="59" spans="2:12" customFormat="1">
+      <c r="B59" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" customFormat="1"/>
+    <row r="66" spans="2:14" s="3" customFormat="1"/>
+    <row r="67" spans="2:14" customFormat="1">
+      <c r="B67" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="2:12">
-      <c r="B62" s="2" t="s">
+    <row r="68" spans="2:14" customFormat="1">
+      <c r="B68" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J62" s="2" t="s">
+      <c r="J68" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L62" s="2" t="s">
+      <c r="L68" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="2:12">
-      <c r="B63" s="2" t="s">
+    <row r="69" spans="2:14" customFormat="1">
+      <c r="B69" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J63" s="2" t="s">
+      <c r="J69" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L63" s="2" t="s">
+      <c r="L69" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="2:12">
-      <c r="B64" s="2" t="s">
+    <row r="70" spans="2:14" customFormat="1">
+      <c r="B70" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J64" s="2" t="s">
+      <c r="J70" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L64" s="2" t="s">
+      <c r="L70" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="65" spans="2:14">
-      <c r="B65" s="2" t="s">
+    <row r="71" spans="2:14" customFormat="1">
+      <c r="B71" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J65" s="2" t="s">
+      <c r="J71" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L65" s="2" t="s">
+      <c r="L71" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="N65" s="2"/>
-    </row>
-    <row r="66" spans="2:14">
-      <c r="J66" s="2"/>
-      <c r="L66" s="2"/>
-      <c r="N66" s="2"/>
-    </row>
-    <row r="67" spans="2:14">
-      <c r="J67" s="2"/>
-      <c r="L67" s="2"/>
-    </row>
-    <row r="70" spans="2:14" s="3" customFormat="1"/>
-    <row r="71" spans="2:14">
-      <c r="B71" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J71" s="2"/>
-      <c r="L71" s="2"/>
       <c r="N71" s="2"/>
     </row>
-    <row r="72" spans="2:14">
-      <c r="B72" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C72" s="2" t="s">
+    <row r="72" spans="2:14" customFormat="1">
+      <c r="J72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="N72" s="2"/>
+    </row>
+    <row r="73" spans="2:14" customFormat="1">
+      <c r="J73" s="2"/>
+      <c r="L73" s="2"/>
+    </row>
+    <row r="76" spans="2:14" s="3" customFormat="1"/>
+    <row r="77" spans="2:14" customFormat="1">
+      <c r="B77" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J72" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14">
-      <c r="B73" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L73" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="74" spans="2:14">
-      <c r="B74" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="75" spans="2:14">
-      <c r="B75" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="76" spans="2:14">
-      <c r="B76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="77" spans="2:14">
-      <c r="B77" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="M77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="L77" s="2"/>
       <c r="N77" s="2"/>
     </row>
-    <row r="78" spans="2:14">
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="L78" s="2"/>
+    <row r="78" spans="2:14" customFormat="1">
+      <c r="B78" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="79" spans="2:14" s="3" customFormat="1"/>
-    <row r="80" spans="2:14">
+    <row r="79" spans="2:14" customFormat="1">
+      <c r="B79" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14" customFormat="1">
       <c r="B80" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C80" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="81" spans="2:12">
+    <row r="81" spans="2:14" customFormat="1">
       <c r="B81" s="2" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>51</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="82" spans="2:12">
+    <row r="82" spans="2:14" customFormat="1">
       <c r="B82" s="2" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>51</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="83" spans="2:12">
+    <row r="83" spans="2:14" customFormat="1">
       <c r="B83" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>76</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
       <c r="J83" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="K83" s="2"/>
       <c r="L83" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="M83" s="2"/>
+      <c r="N83" s="2"/>
     </row>
-    <row r="84" spans="2:12">
+    <row r="84" spans="2:14" customFormat="1">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="L84" s="2"/>
+    </row>
+    <row r="85" spans="2:14" s="3" customFormat="1"/>
+    <row r="86" spans="2:14" customFormat="1">
+      <c r="B86" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C86" s="2"/>
+    </row>
+    <row r="87" spans="2:14" customFormat="1">
+      <c r="B87" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="88" spans="2:14" customFormat="1">
+      <c r="B88" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="89" spans="2:14" customFormat="1">
+      <c r="B89" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" spans="2:14" customFormat="1">
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
   <si>
     <t>##var</t>
   </si>
@@ -637,6 +637,12 @@
   </si>
   <si>
     <t>Task: TaskDebug</t>
+  </si>
+  <si>
+    <t>TaskDoCooldown</t>
+  </si>
+  <si>
+    <t>Task: TaskDoCooldown</t>
   </si>
   <si>
     <t>TaskDoCost</t>
@@ -1071,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="1:109"/>
+  <dimension ref="1:110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1" style="5"/>
@@ -2585,57 +2591,57 @@
         <v>162</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="N104" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9"/>
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="8"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="8"/>
-      <c r="J105" s="8"/>
-      <c r="K105" s="8"/>
-      <c r="L105" s="8"/>
-      <c r="M105" s="8"/>
-      <c r="N105" s="9"/>
+      <c r="B105" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L105" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="N105" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="106">
-      <c r="B106" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>210</v>
-      </c>
+      <c r="A106" s="9"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="8"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+      <c r="M106" s="8"/>
+      <c r="N106" s="9"/>
     </row>
     <row r="107">
       <c r="B107" s="5" t="s">
-        <v>211</v>
+        <v>64</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="G107" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="J107" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L107" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N107" s="3" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="108">
@@ -2652,7 +2658,7 @@
         <v>162</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>150</v>
+        <v>33</v>
       </c>
       <c r="N108" s="3" t="s">
         <v>163</v>
@@ -2675,6 +2681,26 @@
         <v>150</v>
       </c>
       <c r="N109" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L110" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="N110" s="3" t="s">
         <v>163</v>
       </c>
     </row>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t>##var</t>
   </si>
@@ -102,6 +102,24 @@
     <t>EX-GAS内部通用的参数类型，所有自定义泛型类的参数都需要继承自XParam</t>
   </si>
   <si>
+    <t>XParamDodgeMove</t>
+  </si>
+  <si>
+    <t>参数类型: XParamDodgeMove</t>
+  </si>
+  <si>
+    <t>DodgeSpeed</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>WindUpFrames</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>XParamCueList</t>
   </si>
   <si>
@@ -123,9 +141,6 @@
     <t>RotationOffset</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
     <t>XParamCatchAreaBox3D</t>
   </si>
   <si>
@@ -153,9 +168,6 @@
     <t>layer</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>XParamTimeline</t>
   </si>
   <si>
@@ -619,6 +631,12 @@
   </si>
   <si>
     <t>AbilityTask基类</t>
+  </si>
+  <si>
+    <t>TaskDodgeMove</t>
+  </si>
+  <si>
+    <t>Task: TaskDodgeMove</t>
   </si>
   <si>
     <t>TaskPlayCuePreset</t>
@@ -1077,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="1:110"/>
+  <dimension ref="1:114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1" style="5"/>
@@ -1217,73 +1235,71 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="L6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="L8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="J8" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="J9" s="5" t="s">
+      <c r="C10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10">
       <c r="J10" s="5" t="s">
         <v>40</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>40</v>
@@ -1291,78 +1307,76 @@
     </row>
     <row r="11">
       <c r="J11" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="N11" s="3" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="12">
+      <c r="J12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="XFD12" s="6"/>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="s">
+      <c r="J13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="N13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="XFD13" s="6"/>
+    </row>
+    <row r="14">
+      <c r="J14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="XFD13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="G16" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="J15" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N15" s="3" t="s">
+      <c r="G17" s="5" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="J16" s="5" t="s">
+      <c r="J17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="L16" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="J17" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="L17" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>52</v>
@@ -1373,894 +1387,880 @@
         <v>53</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
       <c r="J19" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="J20" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="J21" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="J22" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="J25" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>28</v>
       </c>
       <c r="N25" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="J26" s="5" t="s">
+      <c r="J27" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="L26" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N26" s="3" t="s">
+      <c r="L27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G28" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N28" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="29">
-      <c r="B29" s="5" t="s">
+      <c r="J29" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="L29" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="G31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="J31" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="L31" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32">
       <c r="J32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L32" s="5" t="s">
+      <c r="C33" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>73</v>
+      <c r="J33" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" s="5" t="s">
+      <c r="J34" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J34" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="L34" s="5" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
       <c r="J35" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G37" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N37" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="L37" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="38">
       <c r="J38" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="L38" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="N38" s="3" t="s">
+      <c r="C40" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="39">
-      <c r="J39" s="5" t="s">
+      <c r="J40" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="L39" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N39" s="3" t="s">
+      <c r="L40" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N40" s="3" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="J40" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="41">
       <c r="J41" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42">
       <c r="J42" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43">
       <c r="J43" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44">
       <c r="J44" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45">
       <c r="J45" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46">
       <c r="J46" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47">
       <c r="J47" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48">
       <c r="J48" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49">
       <c r="J49" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50">
       <c r="J50" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51">
       <c r="J51" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L51" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52">
       <c r="J52" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L52" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53">
       <c r="J53" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L53" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="J54" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="L53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N53" s="3" t="s">
+      <c r="L54" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N54" s="3" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="5" t="s">
+      <c r="J55" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G55" s="5" t="s">
+      <c r="L55" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N55" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="L55" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="56">
       <c r="J56" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L56" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="L56" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N56" s="3" t="s">
+      <c r="C58" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="J57" s="5" t="s">
+      <c r="J58" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="L57" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N57" s="3" t="s">
+      <c r="L58" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N58" s="3" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="J58" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="L58" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="59">
       <c r="J59" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="J60" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="L59" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="N59" s="3" t="s">
+      <c r="L60" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N60" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="5" t="s">
+      <c r="J61" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61" s="5" t="s">
+      <c r="L61" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N61" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N61" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="62">
       <c r="J62" s="5" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="L62" s="5" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="L64" s="5" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65">
       <c r="J65" s="5" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="L65" s="5" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G67" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N67" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J67" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L67" s="5" t="s">
+    </row>
+    <row r="68">
+      <c r="J68" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="N67" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="s">
+      <c r="L68" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N68" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="J69" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L69" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N69" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L70" s="5" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>145</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="J71" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L71" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N71" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L73" s="5" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L74" s="5" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="J75" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L75" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N75" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="9"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8"/>
-      <c r="N76" s="9"/>
+      <c r="B76" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L76" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="77">
       <c r="B77" s="5" t="s">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>159</v>
       </c>
+      <c r="J77" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L77" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="78">
       <c r="B78" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="L78" s="5" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="J79" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L79" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="N79" s="3" t="s">
-        <v>163</v>
-      </c>
+      <c r="A79" s="9"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
+      <c r="N79" s="9"/>
     </row>
     <row r="80">
       <c r="B80" s="5" t="s">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L80" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="N80" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L81" s="5" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L82" s="5" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L83" s="5" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L84" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="N84" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G84" s="5" t="s">
+      <c r="C85" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G85" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="J84" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L84" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="N84" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="9"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
-      <c r="N85" s="9"/>
+      <c r="J85" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L85" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="5" t="s">
         <v>176</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>177</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L86" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="87">
@@ -2268,86 +2268,86 @@
         <v>178</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>179</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L87" s="5" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L88" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>163</v>
-      </c>
+      <c r="A88" s="9"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
+      <c r="N88" s="9"/>
     </row>
     <row r="89">
       <c r="B89" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G89" s="5" t="s">
+      <c r="C90" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G90" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="J89" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L89" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="9"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="M90" s="8"/>
-      <c r="N90" s="9"/>
+      <c r="J90" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L90" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="N90" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="91">
       <c r="B91" s="5" t="s">
         <v>184</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>185</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L91" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="92">
@@ -2355,126 +2355,126 @@
         <v>186</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>187</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L92" s="5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L93" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N93" s="3" t="s">
-        <v>163</v>
-      </c>
+      <c r="A93" s="9"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+      <c r="M93" s="8"/>
+      <c r="N93" s="9"/>
     </row>
     <row r="94">
       <c r="B94" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="J94" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L94" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L95" s="5" t="s">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L96" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C96" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G96" s="5" t="s">
+      <c r="C97" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="G97" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="J96" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L96" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="9"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="8"/>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
-      <c r="M97" s="8"/>
-      <c r="N97" s="9"/>
+      <c r="J97" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L97" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="98">
       <c r="B98" s="5" t="s">
         <v>196</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="G98" s="5" t="s">
         <v>197</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L98" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="99">
@@ -2482,226 +2482,293 @@
         <v>198</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="G99" s="5" t="s">
         <v>199</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L99" s="5" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L100" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>163</v>
-      </c>
+      <c r="A100" s="9"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+      <c r="N100" s="9"/>
     </row>
     <row r="101">
       <c r="B101" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="J101" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L101" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L102" s="5" t="s">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L103" s="5" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="N104" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L105" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="N105" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C105" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="G105" s="5" t="s">
+      <c r="C106" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="G106" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J105" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L105" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="9"/>
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="8"/>
-      <c r="M106" s="8"/>
-      <c r="N106" s="9"/>
+      <c r="J106" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L106" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N106" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="107">
       <c r="B107" s="5" t="s">
-        <v>64</v>
+        <v>212</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L107" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N107" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>33</v>
+        <v>154</v>
       </c>
       <c r="N108" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G110" s="5" t="s">
+      <c r="A110" s="9"/>
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="8"/>
+      <c r="F110" s="8"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="8"/>
+      <c r="J110" s="8"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+      <c r="M110" s="8"/>
+      <c r="N110" s="9"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G111" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="J110" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L110" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>163</v>
+    </row>
+    <row r="112">
+      <c r="B112" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L112" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="N112" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L113" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N113" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="J114" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L114" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N114" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
   <si>
     <t>##var</t>
   </si>
@@ -529,6 +529,12 @@
   </si>
   <si>
     <t>参数</t>
+  </si>
+  <si>
+    <t>CueDodgeCooldownUI</t>
+  </si>
+  <si>
+    <t>Cue: CueDodgeCooldownUI</t>
   </si>
   <si>
     <t>CueHitReaction</t>
@@ -1095,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="1:114"/>
+  <dimension ref="1:115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1" style="5"/>
@@ -2177,7 +2183,7 @@
         <v>166</v>
       </c>
       <c r="L82" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="N82" s="3" t="s">
         <v>167</v>
@@ -2197,7 +2203,7 @@
         <v>166</v>
       </c>
       <c r="L83" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>167</v>
@@ -2217,7 +2223,7 @@
         <v>166</v>
       </c>
       <c r="L84" s="5" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="N84" s="3" t="s">
         <v>167</v>
@@ -2237,7 +2243,7 @@
         <v>166</v>
       </c>
       <c r="L85" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>167</v>
@@ -2257,7 +2263,7 @@
         <v>166</v>
       </c>
       <c r="L86" s="5" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>167</v>
@@ -2277,57 +2283,57 @@
         <v>166</v>
       </c>
       <c r="L87" s="5" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="N87" s="3" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="8"/>
-      <c r="M88" s="8"/>
-      <c r="N88" s="9"/>
+      <c r="B88" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L88" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="N88" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="89">
-      <c r="B89" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>181</v>
-      </c>
+      <c r="A89" s="9"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+      <c r="M89" s="8"/>
+      <c r="N89" s="9"/>
     </row>
     <row r="90">
       <c r="B90" s="5" t="s">
         <v>182</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="L90" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N90" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="91">
@@ -2335,7 +2341,7 @@
         <v>184</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>185</v>
@@ -2344,7 +2350,7 @@
         <v>166</v>
       </c>
       <c r="L91" s="5" t="s">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>167</v>
@@ -2355,7 +2361,7 @@
         <v>186</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>187</v>
@@ -2364,57 +2370,57 @@
         <v>166</v>
       </c>
       <c r="L92" s="5" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="N92" s="3" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9"/>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="8"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
-      <c r="M93" s="8"/>
-      <c r="N93" s="9"/>
+      <c r="B93" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L93" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N93" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="94">
-      <c r="B94" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G94" s="5" t="s">
-        <v>189</v>
-      </c>
+      <c r="A94" s="9"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+      <c r="M94" s="8"/>
+      <c r="N94" s="9"/>
     </row>
     <row r="95">
       <c r="B95" s="5" t="s">
         <v>190</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>188</v>
+        <v>23</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="J95" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="L95" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="N95" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="96">
@@ -2422,7 +2428,7 @@
         <v>192</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>193</v>
@@ -2431,7 +2437,7 @@
         <v>166</v>
       </c>
       <c r="L96" s="5" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>167</v>
@@ -2442,7 +2448,7 @@
         <v>194</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G97" s="5" t="s">
         <v>195</v>
@@ -2451,7 +2457,7 @@
         <v>166</v>
       </c>
       <c r="L97" s="5" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>167</v>
@@ -2462,7 +2468,7 @@
         <v>196</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G98" s="5" t="s">
         <v>197</v>
@@ -2471,7 +2477,7 @@
         <v>166</v>
       </c>
       <c r="L98" s="5" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="N98" s="3" t="s">
         <v>167</v>
@@ -2482,7 +2488,7 @@
         <v>198</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G99" s="5" t="s">
         <v>199</v>
@@ -2491,57 +2497,57 @@
         <v>166</v>
       </c>
       <c r="L99" s="5" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9"/>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="8"/>
-      <c r="N100" s="9"/>
+      <c r="B100" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L100" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="101">
-      <c r="B101" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>201</v>
-      </c>
+      <c r="A101" s="9"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+      <c r="M101" s="8"/>
+      <c r="N101" s="9"/>
     </row>
     <row r="102">
       <c r="B102" s="5" t="s">
         <v>202</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="L102" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="103">
@@ -2549,7 +2555,7 @@
         <v>204</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G103" s="5" t="s">
         <v>205</v>
@@ -2558,7 +2564,7 @@
         <v>166</v>
       </c>
       <c r="L103" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N103" s="3" t="s">
         <v>167</v>
@@ -2569,7 +2575,7 @@
         <v>206</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G104" s="5" t="s">
         <v>207</v>
@@ -2578,7 +2584,7 @@
         <v>166</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="N104" s="3" t="s">
         <v>167</v>
@@ -2589,7 +2595,7 @@
         <v>208</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G105" s="5" t="s">
         <v>209</v>
@@ -2598,7 +2604,7 @@
         <v>166</v>
       </c>
       <c r="L105" s="5" t="s">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="N105" s="3" t="s">
         <v>167</v>
@@ -2609,7 +2615,7 @@
         <v>210</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G106" s="5" t="s">
         <v>211</v>
@@ -2618,7 +2624,7 @@
         <v>166</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N106" s="3" t="s">
         <v>167</v>
@@ -2629,7 +2635,7 @@
         <v>212</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G107" s="5" t="s">
         <v>213</v>
@@ -2649,7 +2655,7 @@
         <v>214</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G108" s="5" t="s">
         <v>215</v>
@@ -2669,7 +2675,7 @@
         <v>216</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>217</v>
@@ -2678,57 +2684,57 @@
         <v>166</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="N109" s="3" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8"/>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
-      <c r="M110" s="8"/>
-      <c r="N110" s="9"/>
+      <c r="B110" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L110" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N110" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="111">
-      <c r="B111" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G111" s="5" t="s">
-        <v>218</v>
-      </c>
+      <c r="A111" s="9"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="8"/>
+      <c r="J111" s="8"/>
+      <c r="K111" s="8"/>
+      <c r="L111" s="8"/>
+      <c r="M111" s="8"/>
+      <c r="N111" s="9"/>
     </row>
     <row r="112">
       <c r="B112" s="5" t="s">
-        <v>219</v>
+        <v>68</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="G112" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="J112" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="L112" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N112" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="113">
@@ -2745,7 +2751,7 @@
         <v>166</v>
       </c>
       <c r="L113" s="5" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="N113" s="3" t="s">
         <v>167</v>
@@ -2768,6 +2774,26 @@
         <v>154</v>
       </c>
       <c r="N114" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J115" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L115" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N115" s="3" t="s">
         <v>167</v>
       </c>
     </row>
